--- a/output/pdf_financials_xlsx/GFP.xlsx
+++ b/output/pdf_financials_xlsx/GFP.xlsx
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.675156</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.863416</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.393863</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.337872</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.498899</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.51183</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2031,22 +2031,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>16.678832</v>
+        <v>16.003676</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.30191</v>
+        <v>-5.165326</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.69061</v>
+        <v>-4.084473</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.520285</v>
+        <v>-3.858157</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.301752</v>
+        <v>-2.800651</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.063704</v>
+        <v>-2.575534</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-2.898972</v>
@@ -2147,22 +2147,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>16.678832</v>
+        <v>16.003676</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.30191</v>
+        <v>-5.165326</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.69061</v>
+        <v>-4.084473</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.516607</v>
+        <v>-3.854479</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.301752</v>
+        <v>-2.800651</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.063704</v>
+        <v>-2.575534</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-2.898972</v>
@@ -2458,13 +2458,13 @@
         <v>0.293624</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.0878</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.853689</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>12.911993</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>5.282</v>
@@ -2574,13 +2574,13 @@
         <v>0.293624</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.0878</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.853689</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.33327</v>
+        <v>13.245263</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>5.282</v>
@@ -3270,13 +3270,13 @@
         <v>0.006727</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.094375</v>
+        <v>0.006575</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.860264</v>
+        <v>0.006575</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>12.952214</v>
+        <v>0.040221</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.515</v>
@@ -3285,7 +3285,7 @@
         <v>3.353</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.289</v>
+        <v>80.32299999999999</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>2.647</v>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -60724,7 +60724,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E521" s="5" t="n">

--- a/output/pdf_financials_xlsx/GFP.xlsx
+++ b/output/pdf_financials_xlsx/GFP.xlsx
@@ -1601,16 +1601,16 @@
         <v>-2.25</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-8.162000000000001</v>
+        <v>-10.023</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-0.91</v>
+        <v>-4.132</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-47.019</v>
+        <v>-39.438</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-47.074</v>
+        <v>-21.63</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-98.84399999999999</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-7.581</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-25.444</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>0</v>
@@ -6331,7 +6331,7 @@
         <v>-6.25167</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-6.25167</v>
+        <v>0.047445</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-2.25</v>
@@ -6878,16 +6878,16 @@
         <v>0</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.995</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.928</v>
       </c>
       <c r="Q107" s="3" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.565236</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-0.258</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>0</v>
@@ -28866,7 +28866,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -31446,7 +31450,11 @@
           <t>Share repurchases 17</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -34830,7 +34838,11 @@
           <t>Stock option expense 18</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -39674,7 +39686,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -40993,7 +41009,11 @@
           <t>Issuance of shares and warrants in private placement 17</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -41702,7 +41722,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -44617,7 +44641,11 @@
           <t>Proceed from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -48369,7 +48397,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -48458,7 +48490,11 @@
           <t>Net loss from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -66809,7 +66845,11 @@
           <t>INCOME TAX RECOVERY (Notes 4 and 11)</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
